--- a/outline/Lost_Oracle_outline.xlsx
+++ b/outline/Lost_Oracle_outline.xlsx
@@ -1,20 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\msys64\home\patny\lost-oracle\outline\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{CD027FA4-ED35-4C42-BB79-6642F4F0E1BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D602DD95-CC72-4691-90A1-FC28C59E7922}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{836BA816-2F37-4226-B892-498C904600FD}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
+    <sheet name="Map" sheetId="1" r:id="rId1"/>
+    <sheet name="ToDo" sheetId="3" r:id="rId2"/>
+    <sheet name="Dungeons" sheetId="2" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="137">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="144">
   <si>
     <t>Town</t>
   </si>
@@ -451,14 +452,43 @@
   </si>
   <si>
     <t>Switch hook 2</t>
+  </si>
+  <si>
+    <t>Step</t>
+  </si>
+  <si>
+    <t>Update Link sprite sheet for Farore</t>
+  </si>
+  <si>
+    <t>Sequence for rope</t>
+  </si>
+  <si>
+    <t>Sequence for chart</t>
+  </si>
+  <si>
+    <t>Sequence for (shield)</t>
+  </si>
+  <si>
+    <t>Sequence for (sword)</t>
+  </si>
+  <si>
+    <t>Magical key</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <strike/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
@@ -852,7 +882,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="175">
+  <cellXfs count="172">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -890,10 +920,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -902,7 +929,7 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -931,22 +958,16 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -966,10 +987,10 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="12" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -981,7 +1002,7 @@
     <xf numFmtId="0" fontId="0" fillId="12" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -997,7 +1018,7 @@
     <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="14" borderId="0" xfId="0" applyFill="1"/>
@@ -1010,7 +1031,7 @@
     <xf numFmtId="0" fontId="0" fillId="15" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="15" borderId="0" xfId="0" applyFill="1"/>
@@ -1095,7 +1116,7 @@
     <xf numFmtId="0" fontId="0" fillId="9" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
@@ -1137,7 +1158,7 @@
     <xf numFmtId="0" fontId="0" fillId="17" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="17" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="17" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1158,10 +1179,7 @@
     <xf numFmtId="0" fontId="0" fillId="17" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1201,15 +1219,12 @@
     <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="18" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="18" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1236,7 +1251,7 @@
     <xf numFmtId="0" fontId="0" fillId="7" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1258,7 +1273,7 @@
     <xf numFmtId="0" fontId="0" fillId="19" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="19" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="19" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1339,6 +1354,10 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1679,7 +1698,7 @@
   <cols>
     <col min="1" max="1" width="15.7109375" customWidth="1"/>
     <col min="6" max="6" width="6.85546875" style="1" customWidth="1"/>
-    <col min="7" max="22" width="6.85546875" style="31" customWidth="1"/>
+    <col min="7" max="22" width="6.85546875" style="30" customWidth="1"/>
     <col min="25" max="25" width="18.7109375" bestFit="1" customWidth="1"/>
     <col min="26" max="26" width="19.140625" customWidth="1"/>
     <col min="28" max="44" width="6.28515625" customWidth="1"/>
@@ -1687,7 +1706,7 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:62" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="K2" s="31" t="s">
+      <c r="K2" s="30" t="s">
         <v>41</v>
       </c>
     </row>
@@ -1712,7 +1731,7 @@
         <f>+DEC2HEX(HEX2DEC(G3)+1,2)</f>
         <v>01</v>
       </c>
-      <c r="I3" s="102" t="str">
+      <c r="I3" s="99" t="str">
         <f t="shared" ref="I3:V3" si="0">+DEC2HEX(HEX2DEC(H3)+1,2)</f>
         <v>02</v>
       </c>
@@ -1756,7 +1775,7 @@
         <f t="shared" si="0"/>
         <v>0C</v>
       </c>
-      <c r="T3" s="102" t="str">
+      <c r="T3" s="99" t="str">
         <f t="shared" si="0"/>
         <v>0D</v>
       </c>
@@ -1768,7 +1787,7 @@
         <f t="shared" si="0"/>
         <v>0F</v>
       </c>
-      <c r="Y3" s="122" t="s">
+      <c r="Y3" s="118" t="s">
         <v>39</v>
       </c>
       <c r="AB3" s="1"/>
@@ -1780,7 +1799,7 @@
         <f>+DEC2HEX(HEX2DEC(AC3)+1,2)</f>
         <v>01</v>
       </c>
-      <c r="AE3" s="126" t="str">
+      <c r="AE3" s="1" t="str">
         <f t="shared" ref="AE3:AR3" si="1">+DEC2HEX(HEX2DEC(AD3)+1,2)</f>
         <v>02</v>
       </c>
@@ -1916,12 +1935,12 @@
         <f>+DEC2HEX(HEX2DEC(0),2)</f>
         <v>00</v>
       </c>
-      <c r="G4" s="58" t="s">
+      <c r="G4" s="55" t="s">
         <v>27</v>
       </c>
-      <c r="H4" s="59"/>
-      <c r="I4" s="59"/>
-      <c r="J4" s="99"/>
+      <c r="H4" s="56"/>
+      <c r="I4" s="56"/>
+      <c r="J4" s="96"/>
       <c r="K4" s="12"/>
       <c r="L4" s="12"/>
       <c r="M4" s="12"/>
@@ -1934,32 +1953,32 @@
       <c r="T4" s="12"/>
       <c r="U4" s="12"/>
       <c r="V4" s="13"/>
-      <c r="Y4" s="30" t="s">
+      <c r="Y4" s="29" t="s">
         <v>49</v>
       </c>
-      <c r="Z4" s="30" t="s">
+      <c r="Z4" s="29" t="s">
         <v>47</v>
       </c>
       <c r="AB4" s="1" t="str">
         <f>+DEC2HEX(HEX2DEC(0),2)</f>
         <v>00</v>
       </c>
-      <c r="AC4" s="144"/>
-      <c r="AD4" s="145"/>
-      <c r="AE4" s="145"/>
-      <c r="AF4" s="162"/>
-      <c r="AG4" s="125"/>
-      <c r="AH4" s="125"/>
-      <c r="AI4" s="125"/>
-      <c r="AJ4" s="125"/>
-      <c r="AK4" s="161"/>
-      <c r="AL4" s="140"/>
-      <c r="AM4" s="140"/>
-      <c r="AN4" s="141"/>
-      <c r="AO4" s="109"/>
-      <c r="AP4" s="109"/>
-      <c r="AQ4" s="109"/>
-      <c r="AR4" s="110"/>
+      <c r="AC4" s="139"/>
+      <c r="AD4" s="140"/>
+      <c r="AE4" s="140"/>
+      <c r="AF4" s="157"/>
+      <c r="AG4" s="121"/>
+      <c r="AH4" s="121"/>
+      <c r="AI4" s="121"/>
+      <c r="AJ4" s="121"/>
+      <c r="AK4" s="156"/>
+      <c r="AL4" s="135"/>
+      <c r="AM4" s="135"/>
+      <c r="AN4" s="136"/>
+      <c r="AO4" s="106"/>
+      <c r="AP4" s="106"/>
+      <c r="AQ4" s="106"/>
+      <c r="AR4" s="107"/>
       <c r="AT4" s="1" t="str">
         <f>+DEC2HEX(HEX2DEC(0),2)</f>
         <v>00</v>
@@ -1974,12 +1993,12 @@
       <c r="BB4" s="11"/>
       <c r="BC4" s="11"/>
       <c r="BD4" s="11"/>
-      <c r="BE4" s="16"/>
-      <c r="BF4" s="16"/>
-      <c r="BG4" s="16"/>
-      <c r="BH4" s="16"/>
-      <c r="BI4" s="16"/>
-      <c r="BJ4" s="17"/>
+      <c r="BE4" s="15"/>
+      <c r="BF4" s="15"/>
+      <c r="BG4" s="15"/>
+      <c r="BH4" s="15"/>
+      <c r="BI4" s="15"/>
+      <c r="BJ4" s="16"/>
     </row>
     <row r="5" spans="1:62" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5">
@@ -1995,70 +2014,72 @@
         <f>+DEC2HEX(HEX2DEC(F4)+1,2)</f>
         <v>01</v>
       </c>
-      <c r="G5" s="60"/>
-      <c r="H5" s="61"/>
-      <c r="I5" s="61"/>
-      <c r="J5" s="100"/>
-      <c r="K5" s="16"/>
-      <c r="L5" s="16"/>
-      <c r="M5" s="16"/>
-      <c r="N5" s="16"/>
-      <c r="O5" s="16"/>
-      <c r="P5" s="16"/>
-      <c r="Q5" s="16"/>
-      <c r="R5" s="16"/>
-      <c r="S5" s="16"/>
+      <c r="G5" s="57"/>
+      <c r="H5" s="58"/>
+      <c r="I5" s="58"/>
+      <c r="J5" s="97"/>
+      <c r="K5" s="15"/>
+      <c r="L5" s="15"/>
+      <c r="M5" s="75" t="s">
+        <v>26</v>
+      </c>
+      <c r="N5" s="72"/>
+      <c r="O5" s="72"/>
+      <c r="P5" s="72"/>
+      <c r="Q5" s="73"/>
+      <c r="R5" s="15"/>
+      <c r="S5" s="15"/>
       <c r="T5" s="5" t="s">
         <v>30</v>
       </c>
       <c r="U5" s="6"/>
-      <c r="V5" s="18"/>
+      <c r="V5" s="17"/>
       <c r="Y5" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="Z5" s="129" t="s">
+      <c r="Z5" s="124" t="s">
         <v>43</v>
       </c>
       <c r="AB5" s="1" t="str">
         <f>+DEC2HEX(HEX2DEC(AB4)+1,2)</f>
         <v>01</v>
       </c>
-      <c r="AC5" s="146"/>
-      <c r="AD5" s="147"/>
-      <c r="AE5" s="147"/>
-      <c r="AF5" s="85"/>
-      <c r="AG5" s="35"/>
-      <c r="AH5" s="35"/>
-      <c r="AI5" s="35"/>
-      <c r="AJ5" s="35"/>
-      <c r="AK5" s="93"/>
-      <c r="AL5" s="90"/>
-      <c r="AM5" s="90"/>
-      <c r="AN5" s="142"/>
-      <c r="AO5" s="104"/>
-      <c r="AP5" s="104"/>
-      <c r="AQ5" s="104"/>
-      <c r="AR5" s="105"/>
+      <c r="AC5" s="141"/>
+      <c r="AD5" s="142"/>
+      <c r="AE5" s="142"/>
+      <c r="AF5" s="82"/>
+      <c r="AG5" s="32"/>
+      <c r="AH5" s="32"/>
+      <c r="AI5" s="32"/>
+      <c r="AJ5" s="32"/>
+      <c r="AK5" s="90"/>
+      <c r="AL5" s="87"/>
+      <c r="AM5" s="87"/>
+      <c r="AN5" s="137"/>
+      <c r="AO5" s="101"/>
+      <c r="AP5" s="101"/>
+      <c r="AQ5" s="101"/>
+      <c r="AR5" s="102"/>
       <c r="AT5" s="1" t="str">
         <f>+DEC2HEX(HEX2DEC(AT4)+1,2)</f>
         <v>01</v>
       </c>
       <c r="AU5" s="14"/>
-      <c r="AV5" s="15"/>
-      <c r="AW5" s="15"/>
-      <c r="AX5" s="15"/>
-      <c r="AY5" s="15"/>
-      <c r="AZ5" s="15"/>
-      <c r="BA5" s="15"/>
-      <c r="BB5" s="15"/>
-      <c r="BC5" s="15"/>
-      <c r="BD5" s="15"/>
-      <c r="BE5" s="16"/>
-      <c r="BF5" s="16"/>
-      <c r="BG5" s="16"/>
+      <c r="AV5" s="1"/>
+      <c r="AW5" s="1"/>
+      <c r="AX5" s="1"/>
+      <c r="AY5" s="1"/>
+      <c r="AZ5" s="1"/>
+      <c r="BA5" s="1"/>
+      <c r="BB5" s="1"/>
+      <c r="BC5" s="1"/>
+      <c r="BD5" s="1"/>
+      <c r="BE5" s="15"/>
+      <c r="BF5" s="15"/>
+      <c r="BG5" s="15"/>
       <c r="BH5" s="5"/>
       <c r="BI5" s="6"/>
-      <c r="BJ5" s="18"/>
+      <c r="BJ5" s="17"/>
     </row>
     <row r="6" spans="1:62" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6">
@@ -2070,74 +2091,72 @@
       <c r="D6" t="s">
         <v>58</v>
       </c>
-      <c r="F6" s="102" t="str">
+      <c r="F6" s="99" t="str">
         <f t="shared" ref="F6:F19" si="3">+DEC2HEX(HEX2DEC(F5)+1,2)</f>
         <v>02</v>
       </c>
-      <c r="G6" s="60"/>
-      <c r="H6" s="61"/>
-      <c r="I6" s="61"/>
-      <c r="J6" s="100"/>
-      <c r="K6" s="16"/>
-      <c r="L6" s="16"/>
-      <c r="M6" s="78" t="s">
-        <v>26</v>
-      </c>
-      <c r="N6" s="75"/>
-      <c r="O6" s="75"/>
-      <c r="P6" s="75"/>
-      <c r="Q6" s="76"/>
-      <c r="R6" s="50"/>
-      <c r="S6" s="50"/>
+      <c r="G6" s="57"/>
+      <c r="H6" s="58"/>
+      <c r="I6" s="58"/>
+      <c r="J6" s="97"/>
+      <c r="K6" s="15"/>
+      <c r="L6" s="15"/>
+      <c r="M6" s="76"/>
+      <c r="N6" s="171"/>
+      <c r="O6" s="171"/>
+      <c r="P6" s="171"/>
+      <c r="Q6" s="74"/>
+      <c r="R6" s="47"/>
+      <c r="S6" s="47"/>
       <c r="T6" s="7"/>
-      <c r="U6" s="19"/>
-      <c r="V6" s="20"/>
-      <c r="Y6" s="28" t="s">
+      <c r="U6" s="18"/>
+      <c r="V6" s="19"/>
+      <c r="Y6" s="27" t="s">
         <v>2</v>
       </c>
-      <c r="Z6" s="127" t="s">
+      <c r="Z6" s="122" t="s">
         <v>42</v>
       </c>
       <c r="AB6" s="1" t="str">
         <f t="shared" ref="AB6:AB19" si="4">+DEC2HEX(HEX2DEC(AB5)+1,2)</f>
         <v>02</v>
       </c>
-      <c r="AC6" s="146"/>
-      <c r="AD6" s="147"/>
-      <c r="AE6" s="147"/>
-      <c r="AF6" s="85"/>
-      <c r="AG6" s="35"/>
-      <c r="AH6" s="35"/>
-      <c r="AI6" s="35"/>
-      <c r="AJ6" s="35"/>
-      <c r="AK6" s="93"/>
-      <c r="AL6" s="90"/>
-      <c r="AM6" s="90"/>
-      <c r="AN6" s="142"/>
-      <c r="AO6" s="104"/>
-      <c r="AP6" s="104"/>
-      <c r="AQ6" s="104"/>
-      <c r="AR6" s="105"/>
+      <c r="AC6" s="141"/>
+      <c r="AD6" s="142"/>
+      <c r="AE6" s="142"/>
+      <c r="AF6" s="82"/>
+      <c r="AG6" s="32"/>
+      <c r="AH6" s="32"/>
+      <c r="AI6" s="32"/>
+      <c r="AJ6" s="32"/>
+      <c r="AK6" s="90"/>
+      <c r="AL6" s="87"/>
+      <c r="AM6" s="87"/>
+      <c r="AN6" s="137"/>
+      <c r="AO6" s="101"/>
+      <c r="AP6" s="101"/>
+      <c r="AQ6" s="101"/>
+      <c r="AR6" s="102"/>
       <c r="AT6" s="1" t="str">
         <f t="shared" ref="AT6:AT19" si="5">+DEC2HEX(HEX2DEC(AT5)+1,2)</f>
         <v>02</v>
       </c>
       <c r="AU6" s="14"/>
-      <c r="AV6" s="15"/>
-      <c r="AW6" s="15"/>
-      <c r="AX6" s="15"/>
-      <c r="AY6" s="15"/>
-      <c r="AZ6" s="15"/>
-      <c r="BA6" s="15"/>
-      <c r="BB6" s="15"/>
-      <c r="BC6" s="15"/>
-      <c r="BD6" s="15"/>
-      <c r="BE6" s="16"/>
-      <c r="BF6" s="16"/>
-      <c r="BG6" s="16"/>
+      <c r="AV6" s="1"/>
+      <c r="AW6" s="1"/>
+      <c r="AX6" s="1"/>
+      <c r="AY6" s="1"/>
+      <c r="AZ6" s="1"/>
+      <c r="BA6" s="1"/>
+      <c r="BB6" s="1"/>
+      <c r="BC6" s="1"/>
+      <c r="BD6" s="1"/>
+      <c r="BE6" s="15"/>
+      <c r="BF6" s="15"/>
+      <c r="BG6" s="15"/>
       <c r="BH6" s="7"/>
-      <c r="BI6" s="19"/>
-      <c r="BJ6" s="20"/>
+      <c r="BI6" s="18"/>
+      <c r="BJ6" s="19"/>
     </row>
     <row r="7" spans="1:62" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7">
@@ -2153,68 +2172,68 @@
         <f t="shared" si="3"/>
         <v>03</v>
       </c>
-      <c r="G7" s="97"/>
-      <c r="H7" s="98"/>
-      <c r="I7" s="98"/>
-      <c r="J7" s="101"/>
-      <c r="K7" s="16"/>
-      <c r="L7" s="16"/>
-      <c r="M7" s="79"/>
-      <c r="N7" s="56"/>
-      <c r="O7" s="56"/>
-      <c r="P7" s="56"/>
-      <c r="Q7" s="77"/>
-      <c r="R7" s="50"/>
-      <c r="S7" s="50"/>
+      <c r="G7" s="94"/>
+      <c r="H7" s="95"/>
+      <c r="I7" s="95"/>
+      <c r="J7" s="98"/>
+      <c r="K7" s="15"/>
+      <c r="L7" s="15"/>
+      <c r="M7" s="76"/>
+      <c r="N7" s="53"/>
+      <c r="O7" s="53"/>
+      <c r="P7" s="53"/>
+      <c r="Q7" s="74"/>
+      <c r="R7" s="47"/>
+      <c r="S7" s="47"/>
       <c r="T7" s="8"/>
       <c r="U7" s="9"/>
-      <c r="V7" s="21"/>
-      <c r="Y7" s="27" t="s">
+      <c r="V7" s="20"/>
+      <c r="Y7" s="26" t="s">
         <v>50</v>
       </c>
-      <c r="Z7" s="28" t="s">
+      <c r="Z7" s="27" t="s">
         <v>44</v>
       </c>
       <c r="AB7" s="1" t="str">
         <f t="shared" si="4"/>
         <v>03</v>
       </c>
-      <c r="AC7" s="146"/>
-      <c r="AD7" s="147"/>
-      <c r="AE7" s="163"/>
-      <c r="AF7" s="87"/>
-      <c r="AG7" s="88"/>
-      <c r="AH7" s="88"/>
-      <c r="AI7" s="88"/>
-      <c r="AJ7" s="89"/>
-      <c r="AK7" s="93"/>
-      <c r="AL7" s="90"/>
-      <c r="AM7" s="90"/>
-      <c r="AN7" s="142"/>
-      <c r="AO7" s="104"/>
-      <c r="AP7" s="104"/>
-      <c r="AQ7" s="104"/>
-      <c r="AR7" s="105"/>
+      <c r="AC7" s="141"/>
+      <c r="AD7" s="142"/>
+      <c r="AE7" s="158"/>
+      <c r="AF7" s="84"/>
+      <c r="AG7" s="85"/>
+      <c r="AH7" s="85"/>
+      <c r="AI7" s="85"/>
+      <c r="AJ7" s="86"/>
+      <c r="AK7" s="90"/>
+      <c r="AL7" s="87"/>
+      <c r="AM7" s="87"/>
+      <c r="AN7" s="137"/>
+      <c r="AO7" s="101"/>
+      <c r="AP7" s="101"/>
+      <c r="AQ7" s="101"/>
+      <c r="AR7" s="102"/>
       <c r="AT7" s="1" t="str">
         <f t="shared" si="5"/>
         <v>03</v>
       </c>
       <c r="AU7" s="14"/>
-      <c r="AV7" s="15"/>
-      <c r="AW7" s="15"/>
-      <c r="AX7" s="15"/>
-      <c r="AY7" s="15"/>
-      <c r="AZ7" s="15"/>
-      <c r="BA7" s="15"/>
-      <c r="BB7" s="15"/>
-      <c r="BC7" s="15"/>
-      <c r="BD7" s="15"/>
-      <c r="BE7" s="16"/>
-      <c r="BF7" s="16"/>
-      <c r="BG7" s="16"/>
+      <c r="AV7" s="1"/>
+      <c r="AW7" s="1"/>
+      <c r="AX7" s="1"/>
+      <c r="AY7" s="1"/>
+      <c r="AZ7" s="1"/>
+      <c r="BA7" s="1"/>
+      <c r="BB7" s="1"/>
+      <c r="BC7" s="1"/>
+      <c r="BD7" s="1"/>
+      <c r="BE7" s="15"/>
+      <c r="BF7" s="15"/>
+      <c r="BG7" s="15"/>
       <c r="BH7" s="8"/>
       <c r="BI7" s="9"/>
-      <c r="BJ7" s="21"/>
+      <c r="BJ7" s="20"/>
     </row>
     <row r="8" spans="1:62" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8">
@@ -2233,22 +2252,22 @@
         <f t="shared" si="3"/>
         <v>04</v>
       </c>
-      <c r="G8" s="43"/>
-      <c r="H8" s="16"/>
-      <c r="I8" s="16"/>
-      <c r="J8" s="16"/>
-      <c r="K8" s="16"/>
-      <c r="L8" s="16"/>
-      <c r="M8" s="79"/>
-      <c r="N8" s="56"/>
-      <c r="O8" s="56"/>
-      <c r="P8" s="90"/>
-      <c r="Q8" s="168"/>
-      <c r="R8" s="50"/>
-      <c r="S8" s="50"/>
-      <c r="T8" s="50"/>
-      <c r="U8" s="50"/>
-      <c r="V8" s="51"/>
+      <c r="G8" s="40"/>
+      <c r="H8" s="15"/>
+      <c r="I8" s="15"/>
+      <c r="J8" s="15"/>
+      <c r="K8" s="15"/>
+      <c r="L8" s="15"/>
+      <c r="M8" s="76"/>
+      <c r="N8" s="53"/>
+      <c r="O8" s="53"/>
+      <c r="P8" s="87"/>
+      <c r="Q8" s="163"/>
+      <c r="R8" s="47"/>
+      <c r="S8" s="47"/>
+      <c r="T8" s="47"/>
+      <c r="U8" s="47"/>
+      <c r="V8" s="48"/>
       <c r="Y8" s="4" t="s">
         <v>38</v>
       </c>
@@ -2259,42 +2278,42 @@
         <f t="shared" si="4"/>
         <v>04</v>
       </c>
-      <c r="AC8" s="146"/>
-      <c r="AD8" s="165"/>
-      <c r="AE8" s="16"/>
-      <c r="AF8" s="16"/>
-      <c r="AG8" s="16"/>
-      <c r="AH8" s="16"/>
-      <c r="AI8" s="16"/>
-      <c r="AJ8" s="16"/>
-      <c r="AK8" s="94"/>
-      <c r="AL8" s="90"/>
-      <c r="AM8" s="90"/>
-      <c r="AN8" s="167"/>
-      <c r="AO8" s="104"/>
-      <c r="AP8" s="104"/>
-      <c r="AQ8" s="104"/>
-      <c r="AR8" s="105"/>
+      <c r="AC8" s="141"/>
+      <c r="AD8" s="160"/>
+      <c r="AE8" s="15"/>
+      <c r="AF8" s="15"/>
+      <c r="AG8" s="15"/>
+      <c r="AH8" s="15"/>
+      <c r="AI8" s="15"/>
+      <c r="AJ8" s="15"/>
+      <c r="AK8" s="91"/>
+      <c r="AL8" s="87"/>
+      <c r="AM8" s="87"/>
+      <c r="AN8" s="162"/>
+      <c r="AO8" s="101"/>
+      <c r="AP8" s="101"/>
+      <c r="AQ8" s="101"/>
+      <c r="AR8" s="102"/>
       <c r="AT8" s="1" t="str">
         <f t="shared" si="5"/>
         <v>04</v>
       </c>
       <c r="AU8" s="14"/>
-      <c r="AV8" s="15"/>
-      <c r="AW8" s="15"/>
-      <c r="AX8" s="15"/>
-      <c r="AY8" s="15"/>
-      <c r="AZ8" s="15"/>
-      <c r="BA8" s="15"/>
-      <c r="BB8" s="15"/>
-      <c r="BC8" s="15"/>
-      <c r="BD8" s="15"/>
-      <c r="BE8" s="16"/>
-      <c r="BF8" s="16"/>
-      <c r="BG8" s="16"/>
-      <c r="BH8" s="16"/>
-      <c r="BI8" s="16"/>
-      <c r="BJ8" s="17"/>
+      <c r="AV8" s="1"/>
+      <c r="AW8" s="1"/>
+      <c r="AX8" s="1"/>
+      <c r="AY8" s="1"/>
+      <c r="AZ8" s="1"/>
+      <c r="BA8" s="1"/>
+      <c r="BB8" s="1"/>
+      <c r="BC8" s="1"/>
+      <c r="BD8" s="1"/>
+      <c r="BE8" s="15"/>
+      <c r="BF8" s="15"/>
+      <c r="BG8" s="15"/>
+      <c r="BH8" s="15"/>
+      <c r="BI8" s="15"/>
+      <c r="BJ8" s="16"/>
     </row>
     <row r="9" spans="1:62" ht="28.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9">
@@ -2313,68 +2332,68 @@
         <f t="shared" si="3"/>
         <v>05</v>
       </c>
-      <c r="G9" s="43"/>
-      <c r="H9" s="16"/>
-      <c r="I9" s="16"/>
-      <c r="J9" s="16"/>
-      <c r="K9" s="37"/>
-      <c r="L9" s="37"/>
-      <c r="M9" s="93"/>
-      <c r="N9" s="56"/>
-      <c r="O9" s="56"/>
-      <c r="P9" s="90"/>
-      <c r="Q9" s="169"/>
-      <c r="R9" s="50"/>
-      <c r="S9" s="50"/>
-      <c r="T9" s="50"/>
-      <c r="U9" s="50"/>
-      <c r="V9" s="51"/>
+      <c r="G9" s="40"/>
+      <c r="H9" s="15"/>
+      <c r="I9" s="15"/>
+      <c r="J9" s="15"/>
+      <c r="K9" s="34"/>
+      <c r="L9" s="34"/>
+      <c r="M9" s="90"/>
+      <c r="N9" s="53"/>
+      <c r="O9" s="53"/>
+      <c r="P9" s="87"/>
+      <c r="Q9" s="164"/>
+      <c r="R9" s="47"/>
+      <c r="S9" s="47"/>
+      <c r="T9" s="47"/>
+      <c r="U9" s="47"/>
+      <c r="V9" s="48"/>
       <c r="Y9" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Z9" s="44" t="s">
+      <c r="Z9" s="41" t="s">
         <v>46</v>
       </c>
       <c r="AB9" s="1" t="str">
         <f t="shared" si="4"/>
         <v>05</v>
       </c>
-      <c r="AC9" s="164"/>
-      <c r="AD9" s="166"/>
-      <c r="AE9" s="16"/>
-      <c r="AF9" s="159"/>
-      <c r="AG9" s="73"/>
-      <c r="AH9" s="73"/>
-      <c r="AI9" s="73"/>
-      <c r="AJ9" s="73"/>
-      <c r="AK9" s="157"/>
-      <c r="AL9" s="157"/>
-      <c r="AM9" s="158"/>
-      <c r="AN9" s="17"/>
-      <c r="AO9" s="104"/>
-      <c r="AP9" s="104"/>
-      <c r="AQ9" s="104"/>
-      <c r="AR9" s="105"/>
+      <c r="AC9" s="159"/>
+      <c r="AD9" s="161"/>
+      <c r="AE9" s="15"/>
+      <c r="AF9" s="154"/>
+      <c r="AG9" s="70"/>
+      <c r="AH9" s="70"/>
+      <c r="AI9" s="70"/>
+      <c r="AJ9" s="70"/>
+      <c r="AK9" s="152"/>
+      <c r="AL9" s="152"/>
+      <c r="AM9" s="153"/>
+      <c r="AN9" s="16"/>
+      <c r="AO9" s="101"/>
+      <c r="AP9" s="101"/>
+      <c r="AQ9" s="101"/>
+      <c r="AR9" s="102"/>
       <c r="AT9" s="1" t="str">
         <f t="shared" si="5"/>
         <v>05</v>
       </c>
       <c r="AU9" s="14"/>
-      <c r="AV9" s="15"/>
-      <c r="AW9" s="15"/>
-      <c r="AX9" s="15"/>
-      <c r="AY9" s="15"/>
-      <c r="AZ9" s="15"/>
-      <c r="BA9" s="15"/>
-      <c r="BB9" s="15"/>
-      <c r="BC9" s="15"/>
-      <c r="BD9" s="15"/>
-      <c r="BE9" s="16"/>
-      <c r="BF9" s="16"/>
-      <c r="BG9" s="16"/>
-      <c r="BH9" s="16"/>
-      <c r="BI9" s="16"/>
-      <c r="BJ9" s="17"/>
+      <c r="AV9" s="1"/>
+      <c r="AW9" s="1"/>
+      <c r="AX9" s="1"/>
+      <c r="AY9" s="1"/>
+      <c r="AZ9" s="1"/>
+      <c r="BA9" s="1"/>
+      <c r="BB9" s="1"/>
+      <c r="BC9" s="1"/>
+      <c r="BD9" s="1"/>
+      <c r="BE9" s="15"/>
+      <c r="BF9" s="15"/>
+      <c r="BG9" s="15"/>
+      <c r="BH9" s="15"/>
+      <c r="BI9" s="15"/>
+      <c r="BJ9" s="16"/>
     </row>
     <row r="10" spans="1:62" ht="28.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A10">
@@ -2383,7 +2402,7 @@
       <c r="B10" t="s">
         <v>37</v>
       </c>
-      <c r="C10" s="170" t="s">
+      <c r="C10" s="165" t="s">
         <v>132</v>
       </c>
       <c r="D10" t="s">
@@ -2393,70 +2412,70 @@
         <f t="shared" si="3"/>
         <v>06</v>
       </c>
-      <c r="G10" s="43"/>
-      <c r="H10" s="16"/>
-      <c r="I10" s="81"/>
-      <c r="J10" s="80"/>
-      <c r="K10" s="80"/>
-      <c r="L10" s="80"/>
-      <c r="M10" s="113"/>
-      <c r="N10" s="114"/>
-      <c r="O10" s="114"/>
-      <c r="P10" s="115"/>
-      <c r="Q10" s="73"/>
-      <c r="R10" s="73"/>
-      <c r="S10" s="73"/>
-      <c r="T10" s="74" t="s">
+      <c r="G10" s="40"/>
+      <c r="H10" s="15"/>
+      <c r="I10" s="78"/>
+      <c r="J10" s="77"/>
+      <c r="K10" s="77"/>
+      <c r="L10" s="77"/>
+      <c r="M10" s="109"/>
+      <c r="N10" s="110"/>
+      <c r="O10" s="110"/>
+      <c r="P10" s="111"/>
+      <c r="Q10" s="70"/>
+      <c r="R10" s="70"/>
+      <c r="S10" s="70"/>
+      <c r="T10" s="71" t="s">
         <v>23</v>
       </c>
-      <c r="U10" s="50"/>
-      <c r="V10" s="51"/>
-      <c r="Y10" s="40" t="s">
+      <c r="U10" s="47"/>
+      <c r="V10" s="48"/>
+      <c r="Y10" s="37" t="s">
         <v>17</v>
       </c>
-      <c r="Z10" s="26" t="s">
+      <c r="Z10" s="25" t="s">
         <v>48</v>
       </c>
       <c r="AB10" s="1" t="str">
         <f t="shared" si="4"/>
         <v>06</v>
       </c>
-      <c r="AC10" s="43"/>
-      <c r="AD10" s="16"/>
-      <c r="AE10" s="32"/>
-      <c r="AF10" s="160"/>
-      <c r="AG10" s="139"/>
-      <c r="AH10" s="139"/>
-      <c r="AI10" s="139"/>
-      <c r="AJ10" s="139"/>
-      <c r="AK10" s="130"/>
-      <c r="AL10" s="130"/>
-      <c r="AM10" s="155"/>
-      <c r="AN10" s="17"/>
-      <c r="AO10" s="104"/>
-      <c r="AP10" s="104"/>
-      <c r="AQ10" s="104"/>
-      <c r="AR10" s="105"/>
+      <c r="AC10" s="40"/>
+      <c r="AD10" s="15"/>
+      <c r="AE10" s="31"/>
+      <c r="AF10" s="155"/>
+      <c r="AG10" s="134"/>
+      <c r="AH10" s="134"/>
+      <c r="AI10" s="134"/>
+      <c r="AJ10" s="134"/>
+      <c r="AK10" s="125"/>
+      <c r="AL10" s="125"/>
+      <c r="AM10" s="150"/>
+      <c r="AN10" s="16"/>
+      <c r="AO10" s="101"/>
+      <c r="AP10" s="101"/>
+      <c r="AQ10" s="101"/>
+      <c r="AR10" s="102"/>
       <c r="AT10" s="1" t="str">
         <f t="shared" si="5"/>
         <v>06</v>
       </c>
       <c r="AU10" s="14"/>
-      <c r="AV10" s="15"/>
-      <c r="AW10" s="15"/>
-      <c r="AX10" s="15"/>
-      <c r="AY10" s="15"/>
-      <c r="AZ10" s="15"/>
-      <c r="BA10" s="15"/>
-      <c r="BB10" s="15"/>
-      <c r="BC10" s="15"/>
-      <c r="BD10" s="15"/>
-      <c r="BE10" s="33"/>
-      <c r="BF10" s="33"/>
-      <c r="BG10" s="33"/>
-      <c r="BH10" s="33"/>
-      <c r="BI10" s="33"/>
-      <c r="BJ10" s="34"/>
+      <c r="AV10" s="1"/>
+      <c r="AW10" s="1"/>
+      <c r="AX10" s="1"/>
+      <c r="AY10" s="1"/>
+      <c r="AZ10" s="1"/>
+      <c r="BA10" s="1"/>
+      <c r="BB10" s="1"/>
+      <c r="BC10" s="1"/>
+      <c r="BD10" s="1"/>
+      <c r="BE10" s="1"/>
+      <c r="BF10" s="1"/>
+      <c r="BG10" s="1"/>
+      <c r="BH10" s="1"/>
+      <c r="BI10" s="1"/>
+      <c r="BJ10" s="21"/>
     </row>
     <row r="11" spans="1:62" ht="28.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11">
@@ -2468,139 +2487,142 @@
       <c r="C11" t="s">
         <v>133</v>
       </c>
+      <c r="D11" t="s">
+        <v>143</v>
+      </c>
       <c r="F11" s="1" t="str">
         <f t="shared" si="3"/>
         <v>07</v>
       </c>
-      <c r="G11" s="43"/>
-      <c r="H11" s="16"/>
-      <c r="I11" s="82" t="s">
+      <c r="G11" s="40"/>
+      <c r="H11" s="15"/>
+      <c r="I11" s="79" t="s">
         <v>25</v>
       </c>
-      <c r="J11" s="55"/>
-      <c r="K11" s="55"/>
-      <c r="L11" s="91"/>
-      <c r="M11" s="116"/>
-      <c r="N11" s="112"/>
-      <c r="O11" s="112"/>
-      <c r="P11" s="117"/>
-      <c r="Q11" s="45"/>
-      <c r="R11" s="45"/>
-      <c r="S11" s="45"/>
-      <c r="T11" s="67"/>
-      <c r="U11" s="50"/>
-      <c r="V11" s="51"/>
-      <c r="Y11" s="62" t="s">
+      <c r="J11" s="52"/>
+      <c r="K11" s="52"/>
+      <c r="L11" s="88"/>
+      <c r="M11" s="112"/>
+      <c r="N11" s="88"/>
+      <c r="O11" s="88"/>
+      <c r="P11" s="113"/>
+      <c r="Q11" s="42"/>
+      <c r="R11" s="42"/>
+      <c r="S11" s="42"/>
+      <c r="T11" s="64"/>
+      <c r="U11" s="47"/>
+      <c r="V11" s="48"/>
+      <c r="Y11" s="59" t="s">
         <v>22</v>
       </c>
-      <c r="Z11" s="143" t="s">
+      <c r="Z11" s="138" t="s">
         <v>51</v>
       </c>
       <c r="AB11" s="1" t="str">
         <f t="shared" si="4"/>
         <v>07</v>
       </c>
-      <c r="AC11" s="43"/>
-      <c r="AD11" s="16"/>
-      <c r="AE11" s="32"/>
-      <c r="AF11" s="160"/>
-      <c r="AG11" s="139"/>
-      <c r="AH11" s="139"/>
-      <c r="AI11" s="139"/>
-      <c r="AJ11" s="139"/>
-      <c r="AK11" s="130"/>
-      <c r="AL11" s="130"/>
-      <c r="AM11" s="155"/>
-      <c r="AN11" s="17"/>
-      <c r="AO11" s="104"/>
-      <c r="AP11" s="104"/>
-      <c r="AQ11" s="104"/>
-      <c r="AR11" s="105"/>
+      <c r="AC11" s="40"/>
+      <c r="AD11" s="15"/>
+      <c r="AE11" s="31"/>
+      <c r="AF11" s="155"/>
+      <c r="AG11" s="134"/>
+      <c r="AH11" s="134"/>
+      <c r="AI11" s="134"/>
+      <c r="AJ11" s="134"/>
+      <c r="AK11" s="125"/>
+      <c r="AL11" s="125"/>
+      <c r="AM11" s="150"/>
+      <c r="AN11" s="16"/>
+      <c r="AO11" s="101"/>
+      <c r="AP11" s="101"/>
+      <c r="AQ11" s="101"/>
+      <c r="AR11" s="102"/>
       <c r="AT11" s="1" t="str">
         <f t="shared" si="5"/>
         <v>07</v>
       </c>
       <c r="AU11" s="14"/>
-      <c r="AV11" s="15"/>
-      <c r="AW11" s="15"/>
-      <c r="AX11" s="15"/>
-      <c r="AY11" s="15"/>
-      <c r="AZ11" s="15"/>
-      <c r="BA11" s="15"/>
-      <c r="BB11" s="15"/>
-      <c r="BC11" s="15"/>
-      <c r="BD11" s="15"/>
-      <c r="BE11" s="15"/>
-      <c r="BF11" s="15"/>
-      <c r="BG11" s="15"/>
-      <c r="BH11" s="15"/>
-      <c r="BI11" s="15"/>
-      <c r="BJ11" s="22"/>
+      <c r="AV11" s="1"/>
+      <c r="AW11" s="1"/>
+      <c r="AX11" s="1"/>
+      <c r="AY11" s="1"/>
+      <c r="AZ11" s="1"/>
+      <c r="BA11" s="1"/>
+      <c r="BB11" s="1"/>
+      <c r="BC11" s="1"/>
+      <c r="BD11" s="1"/>
+      <c r="BE11" s="1"/>
+      <c r="BF11" s="1"/>
+      <c r="BG11" s="1"/>
+      <c r="BH11" s="1"/>
+      <c r="BI11" s="1"/>
+      <c r="BJ11" s="21"/>
     </row>
     <row r="12" spans="1:62" ht="28.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="F12" s="1" t="str">
         <f t="shared" si="3"/>
         <v>08</v>
       </c>
-      <c r="G12" s="43"/>
-      <c r="H12" s="16"/>
-      <c r="I12" s="82"/>
-      <c r="J12" s="55"/>
-      <c r="K12" s="55"/>
-      <c r="L12" s="55"/>
-      <c r="M12" s="118"/>
-      <c r="N12" s="119"/>
-      <c r="O12" s="120"/>
-      <c r="P12" s="121"/>
-      <c r="Q12" s="71"/>
-      <c r="R12" s="71"/>
-      <c r="S12" s="71"/>
-      <c r="T12" s="72"/>
-      <c r="U12" s="96"/>
-      <c r="V12" s="51"/>
-      <c r="Y12" s="44" t="s">
+      <c r="G12" s="40"/>
+      <c r="H12" s="15"/>
+      <c r="I12" s="79"/>
+      <c r="J12" s="52"/>
+      <c r="K12" s="52"/>
+      <c r="L12" s="52"/>
+      <c r="M12" s="114"/>
+      <c r="N12" s="115"/>
+      <c r="O12" s="116"/>
+      <c r="P12" s="117"/>
+      <c r="Q12" s="68"/>
+      <c r="R12" s="68"/>
+      <c r="S12" s="68"/>
+      <c r="T12" s="69"/>
+      <c r="U12" s="93"/>
+      <c r="V12" s="48"/>
+      <c r="Y12" s="41" t="s">
         <v>18</v>
       </c>
       <c r="AB12" s="1" t="str">
         <f t="shared" si="4"/>
         <v>08</v>
       </c>
-      <c r="AC12" s="131"/>
-      <c r="AD12" s="132"/>
-      <c r="AE12" s="132"/>
-      <c r="AF12" s="172"/>
-      <c r="AG12" s="173"/>
-      <c r="AH12" s="173"/>
-      <c r="AI12" s="174"/>
-      <c r="AJ12" s="171"/>
-      <c r="AK12" s="154"/>
-      <c r="AL12" s="154"/>
-      <c r="AM12" s="156"/>
-      <c r="AN12" s="17"/>
-      <c r="AO12" s="104"/>
-      <c r="AP12" s="104"/>
-      <c r="AQ12" s="104"/>
-      <c r="AR12" s="105"/>
+      <c r="AC12" s="126"/>
+      <c r="AD12" s="127"/>
+      <c r="AE12" s="127"/>
+      <c r="AF12" s="167"/>
+      <c r="AG12" s="168"/>
+      <c r="AH12" s="168"/>
+      <c r="AI12" s="169"/>
+      <c r="AJ12" s="166"/>
+      <c r="AK12" s="149"/>
+      <c r="AL12" s="149"/>
+      <c r="AM12" s="151"/>
+      <c r="AN12" s="16"/>
+      <c r="AO12" s="101"/>
+      <c r="AP12" s="101"/>
+      <c r="AQ12" s="101"/>
+      <c r="AR12" s="102"/>
       <c r="AT12" s="1" t="str">
         <f t="shared" si="5"/>
         <v>08</v>
       </c>
       <c r="AU12" s="14"/>
-      <c r="AV12" s="15"/>
-      <c r="AW12" s="15"/>
-      <c r="AX12" s="15"/>
-      <c r="AY12" s="15"/>
-      <c r="AZ12" s="15"/>
-      <c r="BA12" s="15"/>
-      <c r="BB12" s="15"/>
-      <c r="BC12" s="15"/>
-      <c r="BD12" s="15"/>
-      <c r="BE12" s="15"/>
-      <c r="BF12" s="15"/>
-      <c r="BG12" s="15"/>
-      <c r="BH12" s="15"/>
-      <c r="BI12" s="15"/>
-      <c r="BJ12" s="22"/>
+      <c r="AV12" s="1"/>
+      <c r="AW12" s="1"/>
+      <c r="AX12" s="1"/>
+      <c r="AY12" s="1"/>
+      <c r="AZ12" s="1"/>
+      <c r="BA12" s="1"/>
+      <c r="BB12" s="1"/>
+      <c r="BC12" s="1"/>
+      <c r="BD12" s="1"/>
+      <c r="BE12" s="1"/>
+      <c r="BF12" s="1"/>
+      <c r="BG12" s="1"/>
+      <c r="BH12" s="1"/>
+      <c r="BI12" s="1"/>
+      <c r="BJ12" s="21"/>
     </row>
     <row r="13" spans="1:62" ht="28.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
@@ -2613,65 +2635,65 @@
         <f t="shared" si="3"/>
         <v>09</v>
       </c>
-      <c r="G13" s="43"/>
-      <c r="H13" s="16"/>
-      <c r="I13" s="82"/>
-      <c r="J13" s="55"/>
-      <c r="K13" s="55"/>
-      <c r="L13" s="86"/>
-      <c r="M13" s="111"/>
-      <c r="N13" s="111"/>
-      <c r="O13" s="112"/>
-      <c r="P13" s="65"/>
-      <c r="Q13" s="37"/>
-      <c r="R13" s="37"/>
-      <c r="S13" s="37"/>
-      <c r="T13" s="50"/>
-      <c r="U13" s="96"/>
-      <c r="V13" s="51"/>
-      <c r="Y13" s="54" t="s">
+      <c r="G13" s="40"/>
+      <c r="H13" s="15"/>
+      <c r="I13" s="79"/>
+      <c r="J13" s="52"/>
+      <c r="K13" s="52"/>
+      <c r="L13" s="83"/>
+      <c r="M13" s="108"/>
+      <c r="N13" s="108"/>
+      <c r="O13" s="88"/>
+      <c r="P13" s="62"/>
+      <c r="Q13" s="34"/>
+      <c r="R13" s="34"/>
+      <c r="S13" s="34"/>
+      <c r="T13" s="47"/>
+      <c r="U13" s="93"/>
+      <c r="V13" s="48"/>
+      <c r="Y13" s="51" t="s">
         <v>19</v>
       </c>
       <c r="AB13" s="1" t="str">
         <f t="shared" si="4"/>
         <v>09</v>
       </c>
-      <c r="AC13" s="134"/>
-      <c r="AD13" s="128"/>
-      <c r="AE13" s="128"/>
-      <c r="AF13" s="128"/>
-      <c r="AG13" s="128"/>
-      <c r="AH13" s="128"/>
-      <c r="AI13" s="135"/>
-      <c r="AJ13" s="32"/>
-      <c r="AK13" s="32"/>
-      <c r="AL13" s="32"/>
-      <c r="AM13" s="16"/>
-      <c r="AN13" s="17"/>
-      <c r="AO13" s="104"/>
-      <c r="AP13" s="104"/>
-      <c r="AQ13" s="104"/>
-      <c r="AR13" s="105"/>
+      <c r="AC13" s="129"/>
+      <c r="AD13" s="123"/>
+      <c r="AE13" s="123"/>
+      <c r="AF13" s="123"/>
+      <c r="AG13" s="123"/>
+      <c r="AH13" s="123"/>
+      <c r="AI13" s="130"/>
+      <c r="AJ13" s="31"/>
+      <c r="AK13" s="31"/>
+      <c r="AL13" s="31"/>
+      <c r="AM13" s="15"/>
+      <c r="AN13" s="16"/>
+      <c r="AO13" s="101"/>
+      <c r="AP13" s="101"/>
+      <c r="AQ13" s="101"/>
+      <c r="AR13" s="102"/>
       <c r="AT13" s="1" t="str">
         <f t="shared" si="5"/>
         <v>09</v>
       </c>
       <c r="AU13" s="14"/>
-      <c r="AV13" s="15"/>
-      <c r="AW13" s="15"/>
-      <c r="AX13" s="15"/>
-      <c r="AY13" s="15"/>
-      <c r="AZ13" s="15"/>
-      <c r="BA13" s="15"/>
-      <c r="BB13" s="15"/>
-      <c r="BC13" s="15"/>
-      <c r="BD13" s="15"/>
-      <c r="BE13" s="15"/>
-      <c r="BF13" s="15"/>
-      <c r="BG13" s="15"/>
-      <c r="BH13" s="15"/>
-      <c r="BI13" s="15"/>
-      <c r="BJ13" s="22"/>
+      <c r="AV13" s="1"/>
+      <c r="AW13" s="1"/>
+      <c r="AX13" s="1"/>
+      <c r="AY13" s="1"/>
+      <c r="AZ13" s="1"/>
+      <c r="BA13" s="1"/>
+      <c r="BB13" s="1"/>
+      <c r="BC13" s="1"/>
+      <c r="BD13" s="1"/>
+      <c r="BE13" s="1"/>
+      <c r="BF13" s="1"/>
+      <c r="BG13" s="1"/>
+      <c r="BH13" s="1"/>
+      <c r="BI13" s="1"/>
+      <c r="BJ13" s="21"/>
     </row>
     <row r="14" spans="1:62" ht="28.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
@@ -2684,65 +2706,65 @@
         <f t="shared" si="3"/>
         <v>0A</v>
       </c>
-      <c r="G14" s="43"/>
-      <c r="H14" s="16"/>
-      <c r="I14" s="82"/>
-      <c r="J14" s="55"/>
-      <c r="K14" s="55"/>
-      <c r="L14" s="85"/>
-      <c r="M14" s="35"/>
-      <c r="N14" s="35"/>
-      <c r="O14" s="90"/>
-      <c r="P14" s="66"/>
-      <c r="Q14" s="37"/>
-      <c r="R14" s="37"/>
-      <c r="S14" s="37"/>
-      <c r="T14" s="50"/>
-      <c r="U14" s="96"/>
-      <c r="V14" s="51"/>
-      <c r="Y14" s="57" t="s">
+      <c r="G14" s="40"/>
+      <c r="H14" s="15"/>
+      <c r="I14" s="79"/>
+      <c r="J14" s="52"/>
+      <c r="K14" s="52"/>
+      <c r="L14" s="82"/>
+      <c r="M14" s="32"/>
+      <c r="N14" s="32"/>
+      <c r="O14" s="87"/>
+      <c r="P14" s="63"/>
+      <c r="Q14" s="34"/>
+      <c r="R14" s="34"/>
+      <c r="S14" s="34"/>
+      <c r="T14" s="47"/>
+      <c r="U14" s="93"/>
+      <c r="V14" s="48"/>
+      <c r="Y14" s="54" t="s">
         <v>21</v>
       </c>
       <c r="AB14" s="1" t="str">
         <f t="shared" si="4"/>
         <v>0A</v>
       </c>
-      <c r="AC14" s="134"/>
-      <c r="AD14" s="128"/>
-      <c r="AE14" s="128"/>
-      <c r="AF14" s="128"/>
-      <c r="AG14" s="128"/>
-      <c r="AH14" s="36"/>
-      <c r="AI14" s="136"/>
-      <c r="AJ14" s="151"/>
-      <c r="AK14" s="152"/>
-      <c r="AL14" s="152"/>
-      <c r="AM14" s="152"/>
-      <c r="AN14" s="153"/>
-      <c r="AO14" s="104"/>
-      <c r="AP14" s="104"/>
-      <c r="AQ14" s="104"/>
-      <c r="AR14" s="105"/>
+      <c r="AC14" s="129"/>
+      <c r="AD14" s="123"/>
+      <c r="AE14" s="123"/>
+      <c r="AF14" s="123"/>
+      <c r="AG14" s="123"/>
+      <c r="AH14" s="33"/>
+      <c r="AI14" s="131"/>
+      <c r="AJ14" s="146"/>
+      <c r="AK14" s="147"/>
+      <c r="AL14" s="147"/>
+      <c r="AM14" s="147"/>
+      <c r="AN14" s="148"/>
+      <c r="AO14" s="101"/>
+      <c r="AP14" s="101"/>
+      <c r="AQ14" s="101"/>
+      <c r="AR14" s="102"/>
       <c r="AT14" s="1" t="str">
         <f t="shared" si="5"/>
         <v>0A</v>
       </c>
       <c r="AU14" s="14"/>
-      <c r="AV14" s="15"/>
-      <c r="AW14" s="15"/>
-      <c r="AX14" s="15"/>
-      <c r="AY14" s="15"/>
-      <c r="AZ14" s="15"/>
-      <c r="BA14" s="15"/>
-      <c r="BB14" s="15"/>
-      <c r="BC14" s="15"/>
-      <c r="BD14" s="15"/>
-      <c r="BE14" s="15"/>
-      <c r="BF14" s="15"/>
-      <c r="BG14" s="15"/>
-      <c r="BH14" s="15"/>
-      <c r="BI14" s="15"/>
-      <c r="BJ14" s="22"/>
+      <c r="AV14" s="1"/>
+      <c r="AW14" s="1"/>
+      <c r="AX14" s="1"/>
+      <c r="AY14" s="1"/>
+      <c r="AZ14" s="1"/>
+      <c r="BA14" s="1"/>
+      <c r="BB14" s="1"/>
+      <c r="BC14" s="1"/>
+      <c r="BD14" s="1"/>
+      <c r="BE14" s="1"/>
+      <c r="BF14" s="1"/>
+      <c r="BG14" s="1"/>
+      <c r="BH14" s="1"/>
+      <c r="BI14" s="1"/>
+      <c r="BJ14" s="21"/>
     </row>
     <row r="15" spans="1:62" ht="28.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
@@ -2755,67 +2777,67 @@
         <f t="shared" si="3"/>
         <v>0B</v>
       </c>
-      <c r="G15" s="43"/>
-      <c r="H15" s="16"/>
-      <c r="I15" s="83"/>
-      <c r="J15" s="84"/>
-      <c r="K15" s="84"/>
-      <c r="L15" s="85"/>
-      <c r="M15" s="35"/>
-      <c r="N15" s="90"/>
-      <c r="O15" s="90"/>
-      <c r="P15" s="66"/>
-      <c r="Q15" s="69"/>
-      <c r="R15" s="69"/>
-      <c r="S15" s="70" t="s">
+      <c r="G15" s="40"/>
+      <c r="H15" s="15"/>
+      <c r="I15" s="80"/>
+      <c r="J15" s="81"/>
+      <c r="K15" s="81"/>
+      <c r="L15" s="82"/>
+      <c r="M15" s="32"/>
+      <c r="N15" s="87"/>
+      <c r="O15" s="87"/>
+      <c r="P15" s="63"/>
+      <c r="Q15" s="66"/>
+      <c r="R15" s="66"/>
+      <c r="S15" s="67" t="s">
         <v>24</v>
       </c>
-      <c r="T15" s="95"/>
-      <c r="U15" s="50"/>
-      <c r="V15" s="51"/>
-      <c r="Y15" s="26" t="s">
+      <c r="T15" s="92"/>
+      <c r="U15" s="47"/>
+      <c r="V15" s="48"/>
+      <c r="Y15" s="25" t="s">
         <v>31</v>
       </c>
       <c r="AB15" s="1" t="str">
         <f t="shared" si="4"/>
         <v>0B</v>
       </c>
-      <c r="AC15" s="148"/>
-      <c r="AD15" s="132"/>
-      <c r="AE15" s="133"/>
-      <c r="AF15" s="128"/>
-      <c r="AG15" s="128"/>
-      <c r="AH15" s="36"/>
-      <c r="AI15" s="136"/>
-      <c r="AJ15" s="46"/>
-      <c r="AK15" s="46"/>
-      <c r="AL15" s="46"/>
-      <c r="AM15" s="46"/>
-      <c r="AN15" s="47"/>
-      <c r="AO15" s="104"/>
-      <c r="AP15" s="104"/>
-      <c r="AQ15" s="104"/>
-      <c r="AR15" s="105"/>
+      <c r="AC15" s="143"/>
+      <c r="AD15" s="127"/>
+      <c r="AE15" s="128"/>
+      <c r="AF15" s="123"/>
+      <c r="AG15" s="123"/>
+      <c r="AH15" s="33"/>
+      <c r="AI15" s="131"/>
+      <c r="AJ15" s="43"/>
+      <c r="AK15" s="43"/>
+      <c r="AL15" s="43"/>
+      <c r="AM15" s="43"/>
+      <c r="AN15" s="44"/>
+      <c r="AO15" s="101"/>
+      <c r="AP15" s="101"/>
+      <c r="AQ15" s="101"/>
+      <c r="AR15" s="102"/>
       <c r="AT15" s="1" t="str">
         <f t="shared" si="5"/>
         <v>0B</v>
       </c>
       <c r="AU15" s="14"/>
-      <c r="AV15" s="15"/>
-      <c r="AW15" s="15"/>
-      <c r="AX15" s="15"/>
-      <c r="AY15" s="15"/>
-      <c r="AZ15" s="15"/>
-      <c r="BA15" s="15"/>
-      <c r="BB15" s="15"/>
-      <c r="BC15" s="15"/>
-      <c r="BD15" s="15"/>
-      <c r="BE15" s="15"/>
-      <c r="BF15" s="15"/>
-      <c r="BG15" s="15"/>
-      <c r="BH15" s="15"/>
-      <c r="BI15" s="15"/>
-      <c r="BJ15" s="22"/>
+      <c r="AV15" s="1"/>
+      <c r="AW15" s="1"/>
+      <c r="AX15" s="1"/>
+      <c r="AY15" s="1"/>
+      <c r="AZ15" s="1"/>
+      <c r="BA15" s="1"/>
+      <c r="BB15" s="1"/>
+      <c r="BC15" s="1"/>
+      <c r="BD15" s="1"/>
+      <c r="BE15" s="1"/>
+      <c r="BF15" s="1"/>
+      <c r="BG15" s="1"/>
+      <c r="BH15" s="1"/>
+      <c r="BI15" s="1"/>
+      <c r="BJ15" s="21"/>
     </row>
     <row r="16" spans="1:62" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
@@ -2825,65 +2847,65 @@
         <f t="shared" si="3"/>
         <v>0C</v>
       </c>
-      <c r="G16" s="43"/>
-      <c r="H16" s="16"/>
-      <c r="I16" s="63"/>
-      <c r="J16" s="63"/>
-      <c r="K16" s="63"/>
-      <c r="L16" s="85"/>
-      <c r="M16" s="35"/>
-      <c r="N16" s="90"/>
-      <c r="O16" s="35"/>
-      <c r="P16" s="66"/>
-      <c r="Q16" s="36"/>
-      <c r="R16" s="36"/>
-      <c r="S16" s="68"/>
-      <c r="T16" s="50"/>
-      <c r="U16" s="50"/>
-      <c r="V16" s="51"/>
-      <c r="Y16" s="29" t="s">
+      <c r="G16" s="40"/>
+      <c r="H16" s="15"/>
+      <c r="I16" s="60"/>
+      <c r="J16" s="60"/>
+      <c r="K16" s="60"/>
+      <c r="L16" s="82"/>
+      <c r="M16" s="32"/>
+      <c r="N16" s="87"/>
+      <c r="O16" s="32"/>
+      <c r="P16" s="63"/>
+      <c r="Q16" s="33"/>
+      <c r="R16" s="33"/>
+      <c r="S16" s="65"/>
+      <c r="T16" s="47"/>
+      <c r="U16" s="47"/>
+      <c r="V16" s="48"/>
+      <c r="Y16" s="28" t="s">
         <v>125</v>
       </c>
       <c r="AB16" s="1" t="str">
         <f t="shared" si="4"/>
         <v>0C</v>
       </c>
-      <c r="AC16" s="149"/>
-      <c r="AD16" s="128"/>
-      <c r="AE16" s="135"/>
-      <c r="AF16" s="128"/>
-      <c r="AG16" s="128"/>
-      <c r="AH16" s="36"/>
-      <c r="AI16" s="136"/>
-      <c r="AJ16" s="46"/>
-      <c r="AK16" s="46"/>
-      <c r="AL16" s="46"/>
-      <c r="AM16" s="46"/>
-      <c r="AN16" s="47"/>
-      <c r="AO16" s="104"/>
-      <c r="AP16" s="104"/>
-      <c r="AQ16" s="104"/>
-      <c r="AR16" s="105"/>
+      <c r="AC16" s="144"/>
+      <c r="AD16" s="123"/>
+      <c r="AE16" s="130"/>
+      <c r="AF16" s="123"/>
+      <c r="AG16" s="123"/>
+      <c r="AH16" s="33"/>
+      <c r="AI16" s="131"/>
+      <c r="AJ16" s="43"/>
+      <c r="AK16" s="43"/>
+      <c r="AL16" s="43"/>
+      <c r="AM16" s="43"/>
+      <c r="AN16" s="44"/>
+      <c r="AO16" s="101"/>
+      <c r="AP16" s="101"/>
+      <c r="AQ16" s="101"/>
+      <c r="AR16" s="102"/>
       <c r="AT16" s="1" t="str">
         <f t="shared" si="5"/>
         <v>0C</v>
       </c>
       <c r="AU16" s="14"/>
-      <c r="AV16" s="15"/>
-      <c r="AW16" s="15"/>
-      <c r="AX16" s="15"/>
-      <c r="AY16" s="15"/>
-      <c r="AZ16" s="15"/>
-      <c r="BA16" s="15"/>
-      <c r="BB16" s="15"/>
-      <c r="BC16" s="15"/>
-      <c r="BD16" s="15"/>
-      <c r="BE16" s="15"/>
-      <c r="BF16" s="15"/>
-      <c r="BG16" s="15"/>
-      <c r="BH16" s="15"/>
-      <c r="BI16" s="15"/>
-      <c r="BJ16" s="22"/>
+      <c r="AV16" s="1"/>
+      <c r="AW16" s="1"/>
+      <c r="AX16" s="1"/>
+      <c r="AY16" s="1"/>
+      <c r="AZ16" s="1"/>
+      <c r="BA16" s="1"/>
+      <c r="BB16" s="1"/>
+      <c r="BC16" s="1"/>
+      <c r="BD16" s="1"/>
+      <c r="BE16" s="1"/>
+      <c r="BF16" s="1"/>
+      <c r="BG16" s="1"/>
+      <c r="BH16" s="1"/>
+      <c r="BI16" s="1"/>
+      <c r="BJ16" s="21"/>
     </row>
     <row r="17" spans="1:62" ht="28.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
@@ -2896,64 +2918,64 @@
         <f t="shared" si="3"/>
         <v>0D</v>
       </c>
-      <c r="G17" s="43"/>
-      <c r="H17" s="16"/>
-      <c r="I17" s="16"/>
-      <c r="J17" s="16"/>
-      <c r="K17" s="16"/>
-      <c r="L17" s="85" t="s">
+      <c r="G17" s="40"/>
+      <c r="H17" s="15"/>
+      <c r="I17" s="15"/>
+      <c r="J17" s="15"/>
+      <c r="K17" s="15"/>
+      <c r="L17" s="82" t="s">
         <v>28</v>
       </c>
-      <c r="M17" s="35"/>
-      <c r="N17" s="90"/>
-      <c r="O17" s="35"/>
-      <c r="P17" s="66"/>
-      <c r="Q17" s="36"/>
-      <c r="R17" s="36"/>
-      <c r="S17" s="68"/>
-      <c r="T17" s="50"/>
-      <c r="U17" s="50"/>
-      <c r="V17" s="51"/>
+      <c r="M17" s="32"/>
+      <c r="N17" s="87"/>
+      <c r="O17" s="32"/>
+      <c r="P17" s="63"/>
+      <c r="Q17" s="33"/>
+      <c r="R17" s="33"/>
+      <c r="S17" s="65"/>
+      <c r="T17" s="47"/>
+      <c r="U17" s="47"/>
+      <c r="V17" s="48"/>
       <c r="AB17" s="1" t="str">
         <f t="shared" si="4"/>
         <v>0D</v>
       </c>
-      <c r="AC17" s="123"/>
-      <c r="AD17" s="39"/>
-      <c r="AE17" s="150"/>
-      <c r="AF17" s="137"/>
-      <c r="AG17" s="137"/>
-      <c r="AH17" s="137"/>
-      <c r="AI17" s="138"/>
-      <c r="AJ17" s="48"/>
-      <c r="AK17" s="48"/>
-      <c r="AL17" s="48"/>
-      <c r="AM17" s="48"/>
-      <c r="AN17" s="49"/>
-      <c r="AO17" s="104"/>
-      <c r="AP17" s="104"/>
-      <c r="AQ17" s="104"/>
-      <c r="AR17" s="105"/>
+      <c r="AC17" s="119"/>
+      <c r="AD17" s="36"/>
+      <c r="AE17" s="145"/>
+      <c r="AF17" s="132"/>
+      <c r="AG17" s="132"/>
+      <c r="AH17" s="132"/>
+      <c r="AI17" s="133"/>
+      <c r="AJ17" s="45"/>
+      <c r="AK17" s="45"/>
+      <c r="AL17" s="45"/>
+      <c r="AM17" s="45"/>
+      <c r="AN17" s="46"/>
+      <c r="AO17" s="101"/>
+      <c r="AP17" s="101"/>
+      <c r="AQ17" s="101"/>
+      <c r="AR17" s="102"/>
       <c r="AT17" s="1" t="str">
         <f t="shared" si="5"/>
         <v>0D</v>
       </c>
       <c r="AU17" s="14"/>
-      <c r="AV17" s="15"/>
-      <c r="AW17" s="15"/>
-      <c r="AX17" s="15"/>
-      <c r="AY17" s="15"/>
-      <c r="AZ17" s="15"/>
-      <c r="BA17" s="15"/>
-      <c r="BB17" s="15"/>
-      <c r="BC17" s="15"/>
-      <c r="BD17" s="15"/>
-      <c r="BE17" s="15"/>
-      <c r="BF17" s="15"/>
-      <c r="BG17" s="15"/>
-      <c r="BH17" s="15"/>
-      <c r="BI17" s="15"/>
-      <c r="BJ17" s="22"/>
+      <c r="AV17" s="1"/>
+      <c r="AW17" s="1"/>
+      <c r="AX17" s="1"/>
+      <c r="AY17" s="1"/>
+      <c r="AZ17" s="1"/>
+      <c r="BA17" s="1"/>
+      <c r="BB17" s="1"/>
+      <c r="BC17" s="1"/>
+      <c r="BD17" s="1"/>
+      <c r="BE17" s="1"/>
+      <c r="BF17" s="1"/>
+      <c r="BG17" s="1"/>
+      <c r="BH17" s="1"/>
+      <c r="BI17" s="1"/>
+      <c r="BJ17" s="21"/>
     </row>
     <row r="18" spans="1:62" ht="28.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
@@ -2966,129 +2988,129 @@
         <f t="shared" si="3"/>
         <v>0E</v>
       </c>
-      <c r="G18" s="43"/>
-      <c r="H18" s="16"/>
-      <c r="I18" s="16"/>
-      <c r="J18" s="16"/>
-      <c r="K18" s="16"/>
-      <c r="L18" s="87"/>
-      <c r="M18" s="88"/>
-      <c r="N18" s="92"/>
-      <c r="O18" s="88"/>
-      <c r="P18" s="89"/>
-      <c r="Q18" s="36"/>
-      <c r="R18" s="39"/>
-      <c r="S18" s="68"/>
-      <c r="T18" s="50"/>
-      <c r="U18" s="50" t="s">
+      <c r="G18" s="40"/>
+      <c r="H18" s="15"/>
+      <c r="I18" s="15"/>
+      <c r="J18" s="15"/>
+      <c r="K18" s="15"/>
+      <c r="L18" s="84"/>
+      <c r="M18" s="85"/>
+      <c r="N18" s="89"/>
+      <c r="O18" s="85"/>
+      <c r="P18" s="86"/>
+      <c r="Q18" s="33"/>
+      <c r="R18" s="36"/>
+      <c r="S18" s="65"/>
+      <c r="T18" s="47"/>
+      <c r="U18" s="47" t="s">
         <v>29</v>
       </c>
-      <c r="V18" s="51"/>
+      <c r="V18" s="48"/>
       <c r="AB18" s="1" t="str">
         <f t="shared" si="4"/>
         <v>0E</v>
       </c>
-      <c r="AC18" s="103"/>
-      <c r="AD18" s="104"/>
-      <c r="AE18" s="104"/>
-      <c r="AF18" s="104"/>
-      <c r="AG18" s="104"/>
-      <c r="AH18" s="104"/>
-      <c r="AI18" s="104"/>
-      <c r="AJ18" s="104"/>
-      <c r="AK18" s="104"/>
-      <c r="AL18" s="104"/>
-      <c r="AM18" s="104"/>
-      <c r="AN18" s="104"/>
-      <c r="AO18" s="104"/>
-      <c r="AP18" s="104"/>
-      <c r="AQ18" s="104"/>
-      <c r="AR18" s="105"/>
+      <c r="AC18" s="100"/>
+      <c r="AD18" s="101"/>
+      <c r="AE18" s="101"/>
+      <c r="AF18" s="101"/>
+      <c r="AG18" s="101"/>
+      <c r="AH18" s="101"/>
+      <c r="AI18" s="101"/>
+      <c r="AJ18" s="101"/>
+      <c r="AK18" s="101"/>
+      <c r="AL18" s="101"/>
+      <c r="AM18" s="101"/>
+      <c r="AN18" s="101"/>
+      <c r="AO18" s="101"/>
+      <c r="AP18" s="101"/>
+      <c r="AQ18" s="101"/>
+      <c r="AR18" s="102"/>
       <c r="AT18" s="1" t="str">
         <f t="shared" si="5"/>
         <v>0E</v>
       </c>
       <c r="AU18" s="14"/>
-      <c r="AV18" s="15"/>
-      <c r="AW18" s="15"/>
-      <c r="AX18" s="15"/>
-      <c r="AY18" s="15"/>
-      <c r="AZ18" s="15"/>
-      <c r="BA18" s="15"/>
-      <c r="BB18" s="15"/>
-      <c r="BC18" s="15"/>
-      <c r="BD18" s="15"/>
-      <c r="BE18" s="15"/>
-      <c r="BF18" s="15"/>
-      <c r="BG18" s="15"/>
-      <c r="BH18" s="15"/>
-      <c r="BI18" s="15"/>
-      <c r="BJ18" s="22"/>
+      <c r="AV18" s="1"/>
+      <c r="AW18" s="1"/>
+      <c r="AX18" s="1"/>
+      <c r="AY18" s="1"/>
+      <c r="AZ18" s="1"/>
+      <c r="BA18" s="1"/>
+      <c r="BB18" s="1"/>
+      <c r="BC18" s="1"/>
+      <c r="BD18" s="1"/>
+      <c r="BE18" s="1"/>
+      <c r="BF18" s="1"/>
+      <c r="BG18" s="1"/>
+      <c r="BH18" s="1"/>
+      <c r="BI18" s="1"/>
+      <c r="BJ18" s="21"/>
     </row>
     <row r="19" spans="1:62" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>63</v>
       </c>
-      <c r="F19" s="102" t="str">
+      <c r="F19" s="99" t="str">
         <f t="shared" si="3"/>
         <v>0F</v>
       </c>
-      <c r="G19" s="64"/>
-      <c r="H19" s="42"/>
-      <c r="I19" s="42"/>
-      <c r="J19" s="42"/>
-      <c r="K19" s="42"/>
-      <c r="L19" s="38"/>
-      <c r="M19" s="38"/>
-      <c r="N19" s="92"/>
-      <c r="O19" s="38"/>
-      <c r="P19" s="38"/>
-      <c r="Q19" s="124"/>
-      <c r="R19" s="41"/>
-      <c r="S19" s="124"/>
-      <c r="T19" s="52"/>
-      <c r="U19" s="52"/>
-      <c r="V19" s="53"/>
+      <c r="G19" s="61"/>
+      <c r="H19" s="39"/>
+      <c r="I19" s="39"/>
+      <c r="J19" s="39"/>
+      <c r="K19" s="39"/>
+      <c r="L19" s="35"/>
+      <c r="M19" s="35"/>
+      <c r="N19" s="89"/>
+      <c r="O19" s="35"/>
+      <c r="P19" s="35"/>
+      <c r="Q19" s="120"/>
+      <c r="R19" s="38"/>
+      <c r="S19" s="120"/>
+      <c r="T19" s="49"/>
+      <c r="U19" s="49"/>
+      <c r="V19" s="50"/>
       <c r="AB19" s="1" t="str">
         <f t="shared" si="4"/>
         <v>0F</v>
       </c>
-      <c r="AC19" s="106"/>
-      <c r="AD19" s="107"/>
-      <c r="AE19" s="107"/>
-      <c r="AF19" s="107"/>
-      <c r="AG19" s="107"/>
-      <c r="AH19" s="107"/>
-      <c r="AI19" s="107"/>
-      <c r="AJ19" s="107"/>
-      <c r="AK19" s="107"/>
-      <c r="AL19" s="107"/>
-      <c r="AM19" s="107"/>
-      <c r="AN19" s="107"/>
-      <c r="AO19" s="107"/>
-      <c r="AP19" s="107"/>
-      <c r="AQ19" s="107"/>
-      <c r="AR19" s="108"/>
+      <c r="AC19" s="103"/>
+      <c r="AD19" s="104"/>
+      <c r="AE19" s="104"/>
+      <c r="AF19" s="104"/>
+      <c r="AG19" s="104"/>
+      <c r="AH19" s="104"/>
+      <c r="AI19" s="104"/>
+      <c r="AJ19" s="104"/>
+      <c r="AK19" s="104"/>
+      <c r="AL19" s="104"/>
+      <c r="AM19" s="104"/>
+      <c r="AN19" s="104"/>
+      <c r="AO19" s="104"/>
+      <c r="AP19" s="104"/>
+      <c r="AQ19" s="104"/>
+      <c r="AR19" s="105"/>
       <c r="AT19" s="1" t="str">
         <f t="shared" si="5"/>
         <v>0F</v>
       </c>
-      <c r="AU19" s="23"/>
-      <c r="AV19" s="24"/>
-      <c r="AW19" s="24"/>
-      <c r="AX19" s="24"/>
-      <c r="AY19" s="24"/>
-      <c r="AZ19" s="24"/>
-      <c r="BA19" s="24"/>
-      <c r="BB19" s="24"/>
-      <c r="BC19" s="24"/>
-      <c r="BD19" s="24"/>
-      <c r="BE19" s="24"/>
-      <c r="BF19" s="24"/>
-      <c r="BG19" s="24"/>
-      <c r="BH19" s="24"/>
-      <c r="BI19" s="24"/>
-      <c r="BJ19" s="25"/>
+      <c r="AU19" s="22"/>
+      <c r="AV19" s="23"/>
+      <c r="AW19" s="23"/>
+      <c r="AX19" s="23"/>
+      <c r="AY19" s="23"/>
+      <c r="AZ19" s="23"/>
+      <c r="BA19" s="23"/>
+      <c r="BB19" s="23"/>
+      <c r="BC19" s="23"/>
+      <c r="BD19" s="23"/>
+      <c r="BE19" s="23"/>
+      <c r="BF19" s="23"/>
+      <c r="BG19" s="23"/>
+      <c r="BH19" s="23"/>
+      <c r="BI19" s="23"/>
+      <c r="BJ19" s="24"/>
     </row>
     <row r="20" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
@@ -3126,7 +3148,7 @@
       <c r="C24" t="s">
         <v>126</v>
       </c>
-      <c r="G24" s="31" t="s">
+      <c r="G24" s="30" t="s">
         <v>4</v>
       </c>
     </row>
@@ -3137,7 +3159,7 @@
       <c r="B25">
         <v>6</v>
       </c>
-      <c r="G25" s="31" t="s">
+      <c r="G25" s="30" t="s">
         <v>5</v>
       </c>
     </row>
@@ -3145,7 +3167,7 @@
       <c r="A26" t="s">
         <v>70</v>
       </c>
-      <c r="G26" s="31" t="s">
+      <c r="G26" s="30" t="s">
         <v>6</v>
       </c>
     </row>
@@ -3156,7 +3178,7 @@
       <c r="B27" t="s">
         <v>134</v>
       </c>
-      <c r="G27" s="31" t="s">
+      <c r="G27" s="30" t="s">
         <v>7</v>
       </c>
     </row>
@@ -3167,7 +3189,7 @@
       <c r="B28">
         <v>5</v>
       </c>
-      <c r="G28" s="31" t="s">
+      <c r="G28" s="30" t="s">
         <v>8</v>
       </c>
     </row>
@@ -3186,7 +3208,7 @@
       <c r="B30">
         <v>4</v>
       </c>
-      <c r="G30" s="31" t="s">
+      <c r="G30" s="30" t="s">
         <v>9</v>
       </c>
     </row>
@@ -3200,7 +3222,7 @@
       <c r="C31" t="s">
         <v>127</v>
       </c>
-      <c r="G31" s="31" t="s">
+      <c r="G31" s="30" t="s">
         <v>13</v>
       </c>
     </row>
@@ -3208,7 +3230,7 @@
       <c r="A32" t="s">
         <v>73</v>
       </c>
-      <c r="G32" s="31" t="s">
+      <c r="G32" s="30" t="s">
         <v>14</v>
       </c>
     </row>
@@ -3219,7 +3241,7 @@
       <c r="B33">
         <v>3</v>
       </c>
-      <c r="G33" s="31" t="s">
+      <c r="G33" s="30" t="s">
         <v>10</v>
       </c>
     </row>
@@ -3230,7 +3252,7 @@
       <c r="B34">
         <v>2</v>
       </c>
-      <c r="G34" s="31" t="s">
+      <c r="G34" s="30" t="s">
         <v>11</v>
       </c>
     </row>
@@ -3249,7 +3271,7 @@
       <c r="B36">
         <v>5</v>
       </c>
-      <c r="G36" s="31" t="s">
+      <c r="G36" s="30" t="s">
         <v>12</v>
       </c>
     </row>
@@ -3260,7 +3282,7 @@
       <c r="B37">
         <v>2</v>
       </c>
-      <c r="G37" s="31" t="s">
+      <c r="G37" s="30" t="s">
         <v>15</v>
       </c>
     </row>
@@ -3295,7 +3317,7 @@
       <c r="B41">
         <v>1</v>
       </c>
-      <c r="G41" s="31" t="s">
+      <c r="G41" s="30" t="s">
         <v>16</v>
       </c>
     </row>
@@ -3316,7 +3338,7 @@
       <c r="A44" t="s">
         <v>85</v>
       </c>
-      <c r="G44" s="31" t="s">
+      <c r="G44" s="30" t="s">
         <v>40</v>
       </c>
     </row>
@@ -3329,7 +3351,7 @@
       <c r="A46" t="s">
         <v>87</v>
       </c>
-      <c r="G46" s="31" t="s">
+      <c r="G46" s="30" t="s">
         <v>59</v>
       </c>
     </row>
@@ -3532,6 +3554,108 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E2616656-6753-4CD3-A5ED-2A41A7BD7065}">
+  <dimension ref="A1:B13"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <f>+ROW(A2)-1</f>
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <f t="shared" ref="A3:A13" si="0">+ROW(A3)-1</f>
+        <v>2</v>
+      </c>
+      <c r="B3" s="170" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="B5" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="B6" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <f t="shared" si="0"/>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <f t="shared" si="0"/>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <f t="shared" si="0"/>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12">
+        <f t="shared" si="0"/>
+        <v>11</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13">
+        <f t="shared" si="0"/>
+        <v>12</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A1C06CCA-EB70-495C-AA0B-A519EDED3721}">
   <dimension ref="B2:D10"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
